--- a/assets/Day Sheet Master.xlsx
+++ b/assets/Day Sheet Master.xlsx
@@ -26,12 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="12">
   <si>
     <t xml:space="preserve">Sunday</t>
   </si>
   <si>
-    <t xml:space="preserve">SHOPPERS:</t>
+    <t xml:space="preserve">DEFAULT:</t>
   </si>
   <si>
     <t xml:space="preserve">In</t>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t xml:space="preserve">Monday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHOPPERS:</t>
   </si>
   <si>
     <t xml:space="preserve">Tuesday</t>
@@ -549,7 +552,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.57"/>
@@ -696,7 +699,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z27"/>
-  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.57"/>
@@ -773,7 +776,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>2</v>
@@ -1030,7 +1033,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.57"/>
@@ -1051,7 +1054,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1107,7 +1110,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>2</v>
@@ -1177,7 +1180,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.57"/>
@@ -1198,7 +1201,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1254,7 +1257,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>2</v>
@@ -1324,7 +1327,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.57"/>
@@ -1345,7 +1348,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1401,7 +1404,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>2</v>
@@ -1471,7 +1474,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.57"/>
@@ -1492,7 +1495,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1548,7 +1551,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>2</v>
@@ -1618,7 +1621,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.43"/>
@@ -1636,7 +1639,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1692,7 +1695,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>2</v>
